--- a/chongli_retail_orders_fy_2025-05-01_2026-04-30.xlsx
+++ b/chongli_retail_orders_fy_2025-05-01_2026-04-30.xlsx
@@ -431,7 +431,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BC262"/>
+  <dimension ref="A1:BD262"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -767,6 +767,11 @@
           <t>正/闭</t>
         </is>
       </c>
+      <c r="BD1" t="inlineStr">
+        <is>
+          <t>七色米订单号</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -893,6 +898,7 @@
           <t>关闭</t>
         </is>
       </c>
+      <c r="BD2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -1019,6 +1025,7 @@
           <t>关闭</t>
         </is>
       </c>
+      <c r="BD3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -1145,6 +1152,7 @@
           <t>关闭</t>
         </is>
       </c>
+      <c r="BD4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -1271,6 +1279,7 @@
           <t>关闭</t>
         </is>
       </c>
+      <c r="BD5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -1397,6 +1406,7 @@
           <t>关闭</t>
         </is>
       </c>
+      <c r="BD6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -1523,6 +1533,7 @@
           <t>正常</t>
         </is>
       </c>
+      <c r="BD7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -1649,6 +1660,7 @@
           <t>关闭</t>
         </is>
       </c>
+      <c r="BD8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -1775,6 +1787,7 @@
           <t>正常</t>
         </is>
       </c>
+      <c r="BD9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -1921,6 +1934,7 @@
           <t>关闭</t>
         </is>
       </c>
+      <c r="BD10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -2087,6 +2101,7 @@
           <t>正常</t>
         </is>
       </c>
+      <c r="BD11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -2253,6 +2268,7 @@
           <t>正常</t>
         </is>
       </c>
+      <c r="BD12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -2399,6 +2415,7 @@
           <t>关闭</t>
         </is>
       </c>
+      <c r="BD13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -2545,6 +2562,7 @@
           <t>关闭</t>
         </is>
       </c>
+      <c r="BD14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -2671,6 +2689,7 @@
           <t>关闭</t>
         </is>
       </c>
+      <c r="BD15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -2797,6 +2816,7 @@
           <t>关闭</t>
         </is>
       </c>
+      <c r="BD16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -2943,6 +2963,7 @@
           <t>正常</t>
         </is>
       </c>
+      <c r="BD17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -3069,6 +3090,7 @@
           <t>关闭</t>
         </is>
       </c>
+      <c r="BD18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -3215,6 +3237,7 @@
           <t>正常</t>
         </is>
       </c>
+      <c r="BD19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -3341,6 +3364,7 @@
           <t>关闭</t>
         </is>
       </c>
+      <c r="BD20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -3512,6 +3536,7 @@
           <t>正常</t>
         </is>
       </c>
+      <c r="BD21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -3638,6 +3663,7 @@
           <t>关闭</t>
         </is>
       </c>
+      <c r="BD22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -3794,6 +3820,7 @@
           <t>正常</t>
         </is>
       </c>
+      <c r="BD23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -3960,6 +3987,7 @@
           <t>正常</t>
         </is>
       </c>
+      <c r="BD24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -4116,6 +4144,7 @@
           <t>正常</t>
         </is>
       </c>
+      <c r="BD25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -4272,6 +4301,7 @@
           <t>正常</t>
         </is>
       </c>
+      <c r="BD26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -4428,6 +4458,7 @@
           <t>正常</t>
         </is>
       </c>
+      <c r="BD27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -4564,6 +4595,7 @@
           <t>关闭</t>
         </is>
       </c>
+      <c r="BD28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -4710,6 +4742,7 @@
           <t>正常</t>
         </is>
       </c>
+      <c r="BD29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -4856,6 +4889,7 @@
           <t>正常</t>
         </is>
       </c>
+      <c r="BD30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -5012,6 +5046,7 @@
           <t>正常</t>
         </is>
       </c>
+      <c r="BD31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
@@ -5178,6 +5213,7 @@
           <t>正常</t>
         </is>
       </c>
+      <c r="BD32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
@@ -5304,6 +5340,7 @@
           <t>关闭</t>
         </is>
       </c>
+      <c r="BD33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -5430,6 +5467,7 @@
           <t>关闭</t>
         </is>
       </c>
+      <c r="BD34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
@@ -5556,6 +5594,7 @@
           <t>关闭</t>
         </is>
       </c>
+      <c r="BD35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
@@ -5682,6 +5721,7 @@
           <t>关闭</t>
         </is>
       </c>
+      <c r="BD36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
@@ -5808,6 +5848,7 @@
           <t>关闭</t>
         </is>
       </c>
+      <c r="BD37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
@@ -5934,6 +5975,7 @@
           <t>关闭</t>
         </is>
       </c>
+      <c r="BD38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
@@ -6060,6 +6102,7 @@
           <t>关闭</t>
         </is>
       </c>
+      <c r="BD39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
@@ -6186,6 +6229,7 @@
           <t>关闭</t>
         </is>
       </c>
+      <c r="BD40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
@@ -6345,6 +6389,11 @@
       <c r="BC41" t="inlineStr">
         <is>
           <t>正常</t>
+        </is>
+      </c>
+      <c r="BD41" t="inlineStr">
+        <is>
+          <t>XSD20251030001A</t>
         </is>
       </c>
     </row>
@@ -6493,6 +6542,7 @@
           <t>关闭</t>
         </is>
       </c>
+      <c r="BD42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
@@ -6639,6 +6689,7 @@
           <t>关闭</t>
         </is>
       </c>
+      <c r="BD43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
@@ -6798,6 +6849,11 @@
       <c r="BC44" t="inlineStr">
         <is>
           <t>正常</t>
+        </is>
+      </c>
+      <c r="BD44" t="inlineStr">
+        <is>
+          <t>XSD20251030002A</t>
         </is>
       </c>
     </row>
@@ -6946,6 +7002,7 @@
           <t>关闭</t>
         </is>
       </c>
+      <c r="BD45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
@@ -7072,6 +7129,7 @@
           <t>关闭</t>
         </is>
       </c>
+      <c r="BD46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
@@ -7213,6 +7271,11 @@
           <t>关闭</t>
         </is>
       </c>
+      <c r="BD47" t="inlineStr">
+        <is>
+          <t>XSD20200209016I</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
@@ -7359,6 +7422,7 @@
           <t>关闭</t>
         </is>
       </c>
+      <c r="BD48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
@@ -7505,6 +7569,7 @@
           <t>关闭</t>
         </is>
       </c>
+      <c r="BD49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
@@ -7681,6 +7746,7 @@
           <t>正常</t>
         </is>
       </c>
+      <c r="BD50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
@@ -7857,6 +7923,7 @@
           <t>正常</t>
         </is>
       </c>
+      <c r="BD51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
@@ -8023,6 +8090,7 @@
           <t>正常</t>
         </is>
       </c>
+      <c r="BD52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
@@ -8199,6 +8267,7 @@
           <t>正常</t>
         </is>
       </c>
+      <c r="BD53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
@@ -8345,6 +8414,7 @@
           <t>关闭</t>
         </is>
       </c>
+      <c r="BD54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
@@ -8491,6 +8561,7 @@
           <t>关闭</t>
         </is>
       </c>
+      <c r="BD55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
@@ -8667,6 +8738,7 @@
           <t>正常</t>
         </is>
       </c>
+      <c r="BD56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
@@ -8843,6 +8915,7 @@
           <t>正常</t>
         </is>
       </c>
+      <c r="BD57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
@@ -9019,6 +9092,7 @@
           <t>正常</t>
         </is>
       </c>
+      <c r="BD58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
@@ -9195,6 +9269,7 @@
           <t>正常</t>
         </is>
       </c>
+      <c r="BD59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
@@ -9371,6 +9446,7 @@
           <t>正常</t>
         </is>
       </c>
+      <c r="BD60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
@@ -9547,6 +9623,7 @@
           <t>正常</t>
         </is>
       </c>
+      <c r="BD61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
@@ -9696,6 +9773,7 @@
           <t>关闭</t>
         </is>
       </c>
+      <c r="BD62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
@@ -9845,6 +9923,7 @@
           <t>关闭</t>
         </is>
       </c>
+      <c r="BD63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
@@ -9994,6 +10073,7 @@
           <t>正常</t>
         </is>
       </c>
+      <c r="BD64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
@@ -10143,6 +10223,7 @@
           <t>正常</t>
         </is>
       </c>
+      <c r="BD65" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
@@ -10322,6 +10403,7 @@
           <t>正常</t>
         </is>
       </c>
+      <c r="BD66" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
@@ -10486,6 +10568,11 @@
           <t>正常</t>
         </is>
       </c>
+      <c r="BD67" t="inlineStr">
+        <is>
+          <t>XSD20251029000I</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
@@ -10650,6 +10737,11 @@
           <t>正常</t>
         </is>
       </c>
+      <c r="BD68" t="inlineStr">
+        <is>
+          <t>XSD20251029001I</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
@@ -10812,6 +10904,11 @@
       <c r="BC69" t="inlineStr">
         <is>
           <t>正常</t>
+        </is>
+      </c>
+      <c r="BD69" t="inlineStr">
+        <is>
+          <t>XSD20251031001I</t>
         </is>
       </c>
     </row>
@@ -10953,6 +11050,11 @@
           <t>关闭</t>
         </is>
       </c>
+      <c r="BD70" t="inlineStr">
+        <is>
+          <t>XSD20251105001I</t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
@@ -11102,6 +11204,7 @@
           <t>关闭</t>
         </is>
       </c>
+      <c r="BD71" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
@@ -11276,6 +11379,11 @@
           <t>正常</t>
         </is>
       </c>
+      <c r="BD72" t="inlineStr">
+        <is>
+          <t>XSD20251107002I</t>
+        </is>
+      </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
@@ -11450,6 +11558,11 @@
           <t>正常</t>
         </is>
       </c>
+      <c r="BD73" t="inlineStr">
+        <is>
+          <t>XSD20251109003I</t>
+        </is>
+      </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
@@ -11612,6 +11725,11 @@
       <c r="BC74" t="inlineStr">
         <is>
           <t>正常</t>
+        </is>
+      </c>
+      <c r="BD74" t="inlineStr">
+        <is>
+          <t>XSD20251109004</t>
         </is>
       </c>
     </row>
@@ -11763,6 +11881,11 @@
           <t>正常</t>
         </is>
       </c>
+      <c r="BD75" t="inlineStr">
+        <is>
+          <t>XSD20251109005</t>
+        </is>
+      </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
@@ -11935,6 +12058,11 @@
       <c r="BC76" t="inlineStr">
         <is>
           <t>正常</t>
+        </is>
+      </c>
+      <c r="BD76" t="inlineStr">
+        <is>
+          <t>XSD20251111000I</t>
         </is>
       </c>
     </row>
@@ -12086,6 +12214,7 @@
           <t>关闭</t>
         </is>
       </c>
+      <c r="BD77" t="inlineStr"/>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
@@ -12230,6 +12359,7 @@
           <t>关闭</t>
         </is>
       </c>
+      <c r="BD78" t="inlineStr"/>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
@@ -12404,6 +12534,11 @@
           <t>正常</t>
         </is>
       </c>
+      <c r="BD79" t="inlineStr">
+        <is>
+          <t>XSD20251116001A</t>
+        </is>
+      </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
@@ -12568,6 +12703,11 @@
           <t>正常</t>
         </is>
       </c>
+      <c r="BD80" t="inlineStr">
+        <is>
+          <t>XSD20251117000I</t>
+        </is>
+      </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
@@ -12732,6 +12872,11 @@
           <t>正常</t>
         </is>
       </c>
+      <c r="BD81" t="inlineStr">
+        <is>
+          <t>XSD20251117001I</t>
+        </is>
+      </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
@@ -12896,6 +13041,11 @@
           <t>正常</t>
         </is>
       </c>
+      <c r="BD82" t="inlineStr">
+        <is>
+          <t>XSD20251123002I</t>
+        </is>
+      </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
@@ -13070,6 +13220,11 @@
           <t>正常</t>
         </is>
       </c>
+      <c r="BD83" t="inlineStr">
+        <is>
+          <t>XSD20251123003I</t>
+        </is>
+      </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
@@ -13244,6 +13399,11 @@
           <t>正常</t>
         </is>
       </c>
+      <c r="BD84" t="inlineStr">
+        <is>
+          <t>XSD20251124001I</t>
+        </is>
+      </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
@@ -13418,6 +13578,11 @@
           <t>正常</t>
         </is>
       </c>
+      <c r="BD85" t="inlineStr">
+        <is>
+          <t>XSD20251126003I</t>
+        </is>
+      </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
@@ -13582,6 +13747,11 @@
           <t>正常</t>
         </is>
       </c>
+      <c r="BD86" t="inlineStr">
+        <is>
+          <t>XSD20251126000I</t>
+        </is>
+      </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
@@ -13756,6 +13926,11 @@
           <t>正常</t>
         </is>
       </c>
+      <c r="BD87" t="inlineStr">
+        <is>
+          <t>XSD20251126005I</t>
+        </is>
+      </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
@@ -13920,6 +14095,11 @@
           <t>正常</t>
         </is>
       </c>
+      <c r="BD88" t="inlineStr">
+        <is>
+          <t>XSD20251127001A</t>
+        </is>
+      </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
@@ -14079,6 +14259,11 @@
           <t>正常</t>
         </is>
       </c>
+      <c r="BD89" t="inlineStr">
+        <is>
+          <t>XSD20251127003I</t>
+        </is>
+      </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
@@ -14253,6 +14438,11 @@
           <t>正常</t>
         </is>
       </c>
+      <c r="BD90" t="inlineStr">
+        <is>
+          <t>XSD20251128001A</t>
+        </is>
+      </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
@@ -14425,6 +14615,11 @@
       <c r="BC91" t="inlineStr">
         <is>
           <t>正常</t>
+        </is>
+      </c>
+      <c r="BD91" t="inlineStr">
+        <is>
+          <t>XSD20251128002I</t>
         </is>
       </c>
     </row>
@@ -14576,6 +14771,7 @@
           <t>关闭</t>
         </is>
       </c>
+      <c r="BD92" t="inlineStr"/>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
@@ -14738,6 +14934,11 @@
       <c r="BC93" t="inlineStr">
         <is>
           <t>正常</t>
+        </is>
+      </c>
+      <c r="BD93" t="inlineStr">
+        <is>
+          <t>XSD20251128003I</t>
         </is>
       </c>
     </row>
@@ -14889,6 +15090,7 @@
           <t>关闭</t>
         </is>
       </c>
+      <c r="BD94" t="inlineStr"/>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
@@ -15068,6 +15270,7 @@
           <t>正常</t>
         </is>
       </c>
+      <c r="BD95" t="inlineStr"/>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
@@ -15242,6 +15445,11 @@
           <t>正常</t>
         </is>
       </c>
+      <c r="BD96" t="inlineStr">
+        <is>
+          <t>XSD20251201004A</t>
+        </is>
+      </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
@@ -15406,6 +15614,11 @@
           <t>正常</t>
         </is>
       </c>
+      <c r="BD97" t="inlineStr">
+        <is>
+          <t>XSD20251202000I</t>
+        </is>
+      </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
@@ -15570,6 +15783,11 @@
           <t>正常</t>
         </is>
       </c>
+      <c r="BD98" t="inlineStr">
+        <is>
+          <t>XSD20251202002I</t>
+        </is>
+      </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
@@ -15724,6 +15942,11 @@
           <t>正常</t>
         </is>
       </c>
+      <c r="BD99" t="inlineStr">
+        <is>
+          <t>XSD20251202003I</t>
+        </is>
+      </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
@@ -15888,6 +16111,11 @@
           <t>正常</t>
         </is>
       </c>
+      <c r="BD100" t="inlineStr">
+        <is>
+          <t>XSD20251204000A</t>
+        </is>
+      </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
@@ -16062,6 +16290,11 @@
           <t>正常</t>
         </is>
       </c>
+      <c r="BD101" t="inlineStr">
+        <is>
+          <t>XSD20251204002A</t>
+        </is>
+      </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
@@ -16234,6 +16467,11 @@
       <c r="BC102" t="inlineStr">
         <is>
           <t>正常</t>
+        </is>
+      </c>
+      <c r="BD102" t="inlineStr">
+        <is>
+          <t>XSD20251204003A</t>
         </is>
       </c>
     </row>
@@ -16385,6 +16623,7 @@
           <t>关闭</t>
         </is>
       </c>
+      <c r="BD103" t="inlineStr"/>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
@@ -16534,6 +16773,11 @@
           <t>关闭</t>
         </is>
       </c>
+      <c r="BD104" t="inlineStr">
+        <is>
+          <t>XSD20251205003I</t>
+        </is>
+      </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
@@ -16708,6 +16952,11 @@
           <t>正常</t>
         </is>
       </c>
+      <c r="BD105" t="inlineStr">
+        <is>
+          <t>XSD20251205001I</t>
+        </is>
+      </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
@@ -16872,6 +17121,11 @@
           <t>正常</t>
         </is>
       </c>
+      <c r="BD106" t="inlineStr">
+        <is>
+          <t>XSD20251208000I</t>
+        </is>
+      </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
@@ -17036,6 +17290,7 @@
           <t>正常</t>
         </is>
       </c>
+      <c r="BD107" t="inlineStr"/>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
@@ -17210,6 +17465,11 @@
           <t>正常</t>
         </is>
       </c>
+      <c r="BD108" t="inlineStr">
+        <is>
+          <t>XSD20251211002A</t>
+        </is>
+      </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
@@ -17379,6 +17639,7 @@
           <t>正常</t>
         </is>
       </c>
+      <c r="BD109" t="inlineStr"/>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
@@ -17518,6 +17779,7 @@
           <t>关闭</t>
         </is>
       </c>
+      <c r="BD110" t="inlineStr"/>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
@@ -17677,6 +17939,11 @@
           <t>正常</t>
         </is>
       </c>
+      <c r="BD111" t="inlineStr">
+        <is>
+          <t>XSD20251213007I</t>
+        </is>
+      </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
@@ -17836,6 +18103,11 @@
           <t>正常</t>
         </is>
       </c>
+      <c r="BD112" t="inlineStr">
+        <is>
+          <t>XSD20251213008I</t>
+        </is>
+      </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
@@ -18010,6 +18282,11 @@
           <t>正常</t>
         </is>
       </c>
+      <c r="BD113" t="inlineStr">
+        <is>
+          <t>XSD20251214005A</t>
+        </is>
+      </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
@@ -18184,6 +18461,11 @@
           <t>正常</t>
         </is>
       </c>
+      <c r="BD114" t="inlineStr">
+        <is>
+          <t>XSD20251214010A</t>
+        </is>
+      </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
@@ -18338,6 +18620,11 @@
           <t>正常</t>
         </is>
       </c>
+      <c r="BD115" t="inlineStr">
+        <is>
+          <t>XSD20251214011I</t>
+        </is>
+      </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
@@ -18492,6 +18779,11 @@
           <t>正常</t>
         </is>
       </c>
+      <c r="BD116" t="inlineStr">
+        <is>
+          <t>XSD20251216000I</t>
+        </is>
+      </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
@@ -18646,6 +18938,11 @@
           <t>正常</t>
         </is>
       </c>
+      <c r="BD117" t="inlineStr">
+        <is>
+          <t>XSD20251216001I</t>
+        </is>
+      </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
@@ -18800,6 +19097,11 @@
           <t>正常</t>
         </is>
       </c>
+      <c r="BD118" t="inlineStr">
+        <is>
+          <t>XSD20251217000I</t>
+        </is>
+      </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
@@ -18964,6 +19266,11 @@
           <t>正常</t>
         </is>
       </c>
+      <c r="BD119" t="inlineStr">
+        <is>
+          <t>XSD20251214000I</t>
+        </is>
+      </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
@@ -19138,6 +19445,11 @@
           <t>正常</t>
         </is>
       </c>
+      <c r="BD120" t="inlineStr">
+        <is>
+          <t>XSD20251219000I</t>
+        </is>
+      </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
@@ -19312,6 +19624,11 @@
           <t>正常</t>
         </is>
       </c>
+      <c r="BD121" t="inlineStr">
+        <is>
+          <t>XSD20251220000I</t>
+        </is>
+      </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
@@ -19486,6 +19803,11 @@
           <t>正常</t>
         </is>
       </c>
+      <c r="BD122" t="inlineStr">
+        <is>
+          <t>XSD20251221006A</t>
+        </is>
+      </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
@@ -19660,6 +19982,11 @@
           <t>正常</t>
         </is>
       </c>
+      <c r="BD123" t="inlineStr">
+        <is>
+          <t>XSD20251221007A</t>
+        </is>
+      </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
@@ -19834,6 +20161,11 @@
           <t>正常</t>
         </is>
       </c>
+      <c r="BD124" t="inlineStr">
+        <is>
+          <t>XSD20251221010I</t>
+        </is>
+      </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
@@ -20008,6 +20340,11 @@
           <t>正常</t>
         </is>
       </c>
+      <c r="BD125" t="inlineStr">
+        <is>
+          <t>XSD20251221009I</t>
+        </is>
+      </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
@@ -20160,6 +20497,11 @@
       <c r="BC126" t="inlineStr">
         <is>
           <t>正常</t>
+        </is>
+      </c>
+      <c r="BD126" t="inlineStr">
+        <is>
+          <t>XSD20251221008I</t>
         </is>
       </c>
     </row>
@@ -20311,6 +20653,7 @@
           <t>关闭</t>
         </is>
       </c>
+      <c r="BD127" t="inlineStr"/>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
@@ -20475,6 +20818,11 @@
           <t>正常</t>
         </is>
       </c>
+      <c r="BD128" t="inlineStr">
+        <is>
+          <t>XSD20251222003A</t>
+        </is>
+      </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
@@ -20649,6 +20997,11 @@
           <t>正常</t>
         </is>
       </c>
+      <c r="BD129" t="inlineStr">
+        <is>
+          <t>XSD20251222004A</t>
+        </is>
+      </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
@@ -20803,6 +21156,11 @@
           <t>正常</t>
         </is>
       </c>
+      <c r="BD130" t="inlineStr">
+        <is>
+          <t>XSD20251223002I</t>
+        </is>
+      </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
@@ -20957,6 +21315,11 @@
           <t>正常</t>
         </is>
       </c>
+      <c r="BD131" t="inlineStr">
+        <is>
+          <t>XSD20251223005I</t>
+        </is>
+      </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
@@ -21121,6 +21484,7 @@
           <t>正常</t>
         </is>
       </c>
+      <c r="BD132" t="inlineStr"/>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
@@ -21295,6 +21659,11 @@
           <t>正常</t>
         </is>
       </c>
+      <c r="BD133" t="inlineStr">
+        <is>
+          <t>XSD20251224005A</t>
+        </is>
+      </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
@@ -21464,6 +21833,11 @@
           <t>正常</t>
         </is>
       </c>
+      <c r="BD134" t="inlineStr">
+        <is>
+          <t>XSD20251226002A</t>
+        </is>
+      </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
@@ -21638,6 +22012,11 @@
           <t>正常</t>
         </is>
       </c>
+      <c r="BD135" t="inlineStr">
+        <is>
+          <t>XSD20251226005I</t>
+        </is>
+      </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
@@ -21812,6 +22191,11 @@
           <t>正常</t>
         </is>
       </c>
+      <c r="BD136" t="inlineStr">
+        <is>
+          <t>XSD20251228009I</t>
+        </is>
+      </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
@@ -21986,6 +22370,11 @@
           <t>正常</t>
         </is>
       </c>
+      <c r="BD137" t="inlineStr">
+        <is>
+          <t>XSD20251227012A</t>
+        </is>
+      </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
@@ -22150,6 +22539,11 @@
           <t>正常</t>
         </is>
       </c>
+      <c r="BD138" t="inlineStr">
+        <is>
+          <t>XSD20251228008I</t>
+        </is>
+      </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
@@ -22324,6 +22718,11 @@
           <t>正常</t>
         </is>
       </c>
+      <c r="BD139" t="inlineStr">
+        <is>
+          <t>XSD20251228005A</t>
+        </is>
+      </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
@@ -22478,6 +22877,11 @@
           <t>正常</t>
         </is>
       </c>
+      <c r="BD140" t="inlineStr">
+        <is>
+          <t>XSD20251228010I</t>
+        </is>
+      </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
@@ -22642,6 +23046,11 @@
           <t>正常</t>
         </is>
       </c>
+      <c r="BD141" t="inlineStr">
+        <is>
+          <t>XSD20251228011I</t>
+        </is>
+      </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
@@ -22801,6 +23210,11 @@
           <t>正常</t>
         </is>
       </c>
+      <c r="BD142" t="inlineStr">
+        <is>
+          <t>XSD20251229003I</t>
+        </is>
+      </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
@@ -22975,6 +23389,11 @@
           <t>正常</t>
         </is>
       </c>
+      <c r="BD143" t="inlineStr">
+        <is>
+          <t>XSD20251231012A</t>
+        </is>
+      </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
@@ -23144,6 +23563,7 @@
           <t>正常</t>
         </is>
       </c>
+      <c r="BD144" t="inlineStr"/>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
@@ -23318,6 +23738,11 @@
           <t>正常</t>
         </is>
       </c>
+      <c r="BD145" t="inlineStr">
+        <is>
+          <t>XSD20260101027A</t>
+        </is>
+      </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
@@ -23492,6 +23917,11 @@
           <t>正常</t>
         </is>
       </c>
+      <c r="BD146" t="inlineStr">
+        <is>
+          <t>XSD20260101015A</t>
+        </is>
+      </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
@@ -23666,6 +24096,11 @@
           <t>正常</t>
         </is>
       </c>
+      <c r="BD147" t="inlineStr">
+        <is>
+          <t>XSD20260101020A</t>
+        </is>
+      </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
@@ -23840,6 +24275,11 @@
           <t>正常</t>
         </is>
       </c>
+      <c r="BD148" t="inlineStr">
+        <is>
+          <t>XSD20260101022A</t>
+        </is>
+      </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
@@ -24012,6 +24452,11 @@
       <c r="BC149" t="inlineStr">
         <is>
           <t>正常</t>
+        </is>
+      </c>
+      <c r="BD149" t="inlineStr">
+        <is>
+          <t>XSD20260101026A</t>
         </is>
       </c>
     </row>
@@ -24163,6 +24608,11 @@
           <t>正常</t>
         </is>
       </c>
+      <c r="BD150" t="inlineStr">
+        <is>
+          <t>XSD20260102002I</t>
+        </is>
+      </c>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
@@ -24337,6 +24787,11 @@
           <t>正常</t>
         </is>
       </c>
+      <c r="BD151" t="inlineStr">
+        <is>
+          <t>XSD20260102012A</t>
+        </is>
+      </c>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
@@ -24511,6 +24966,11 @@
           <t>正常</t>
         </is>
       </c>
+      <c r="BD152" t="inlineStr">
+        <is>
+          <t>XSD20260104004A</t>
+        </is>
+      </c>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
@@ -24685,6 +25145,11 @@
           <t>正常</t>
         </is>
       </c>
+      <c r="BD153" t="inlineStr">
+        <is>
+          <t>XSD20260107000I</t>
+        </is>
+      </c>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
@@ -24859,6 +25324,11 @@
           <t>正常</t>
         </is>
       </c>
+      <c r="BD154" t="inlineStr">
+        <is>
+          <t>XSD20260107001I</t>
+        </is>
+      </c>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
@@ -25023,6 +25493,11 @@
           <t>正常</t>
         </is>
       </c>
+      <c r="BD155" t="inlineStr">
+        <is>
+          <t>XSD20260108001I</t>
+        </is>
+      </c>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
@@ -25187,6 +25662,11 @@
           <t>正常</t>
         </is>
       </c>
+      <c r="BD156" t="inlineStr">
+        <is>
+          <t>XSD20260108002A</t>
+        </is>
+      </c>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
@@ -25361,6 +25841,11 @@
           <t>正常</t>
         </is>
       </c>
+      <c r="BD157" t="inlineStr">
+        <is>
+          <t>XSD20260110001A</t>
+        </is>
+      </c>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
@@ -25535,6 +26020,11 @@
           <t>正常</t>
         </is>
       </c>
+      <c r="BD158" t="inlineStr">
+        <is>
+          <t>XSD20260110014A</t>
+        </is>
+      </c>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
@@ -25709,6 +26199,11 @@
           <t>正常</t>
         </is>
       </c>
+      <c r="BD159" t="inlineStr">
+        <is>
+          <t>XSD20260111008A</t>
+        </is>
+      </c>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
@@ -25873,6 +26368,11 @@
           <t>正常</t>
         </is>
       </c>
+      <c r="BD160" t="inlineStr">
+        <is>
+          <t>XSD20260112003I</t>
+        </is>
+      </c>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
@@ -26047,6 +26547,11 @@
           <t>正常</t>
         </is>
       </c>
+      <c r="BD161" t="inlineStr">
+        <is>
+          <t>XSD20260112002A</t>
+        </is>
+      </c>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr">
@@ -26201,6 +26706,11 @@
           <t>正常</t>
         </is>
       </c>
+      <c r="BD162" t="inlineStr">
+        <is>
+          <t>XSD20260114005I</t>
+        </is>
+      </c>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr">
@@ -26365,6 +26875,11 @@
           <t>正常</t>
         </is>
       </c>
+      <c r="BD163" t="inlineStr">
+        <is>
+          <t>XSD20260116007A</t>
+        </is>
+      </c>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr">
@@ -26539,6 +27054,7 @@
           <t>正常</t>
         </is>
       </c>
+      <c r="BD164" t="inlineStr"/>
     </row>
     <row r="165">
       <c r="A165" t="inlineStr">
@@ -26713,6 +27229,11 @@
           <t>正常</t>
         </is>
       </c>
+      <c r="BD165" t="inlineStr">
+        <is>
+          <t>XSD20260119000A</t>
+        </is>
+      </c>
     </row>
     <row r="166">
       <c r="A166" t="inlineStr">
@@ -26887,6 +27408,11 @@
           <t>正常</t>
         </is>
       </c>
+      <c r="BD166" t="inlineStr">
+        <is>
+          <t>XSD20260119001A</t>
+        </is>
+      </c>
     </row>
     <row r="167">
       <c r="A167" t="inlineStr">
@@ -27061,6 +27587,11 @@
           <t>正常</t>
         </is>
       </c>
+      <c r="BD167" t="inlineStr">
+        <is>
+          <t>XSD20260123007A</t>
+        </is>
+      </c>
     </row>
     <row r="168">
       <c r="A168" t="inlineStr">
@@ -27225,6 +27756,11 @@
           <t>正常</t>
         </is>
       </c>
+      <c r="BD168" t="inlineStr">
+        <is>
+          <t>XSD20260124006A</t>
+        </is>
+      </c>
     </row>
     <row r="169">
       <c r="A169" t="inlineStr">
@@ -27399,6 +27935,11 @@
           <t>正常</t>
         </is>
       </c>
+      <c r="BD169" t="inlineStr">
+        <is>
+          <t>XSD20260125013A</t>
+        </is>
+      </c>
     </row>
     <row r="170">
       <c r="A170" t="inlineStr">
@@ -27573,6 +28114,11 @@
           <t>正常</t>
         </is>
       </c>
+      <c r="BD170" t="inlineStr">
+        <is>
+          <t>XSD20260124011A</t>
+        </is>
+      </c>
     </row>
     <row r="171">
       <c r="A171" t="inlineStr">
@@ -27747,6 +28293,11 @@
           <t>正常</t>
         </is>
       </c>
+      <c r="BD171" t="inlineStr">
+        <is>
+          <t>XSD20260126007A</t>
+        </is>
+      </c>
     </row>
     <row r="172">
       <c r="A172" t="inlineStr">
@@ -27921,6 +28472,11 @@
           <t>正常</t>
         </is>
       </c>
+      <c r="BD172" t="inlineStr">
+        <is>
+          <t>XSD20260126006A</t>
+        </is>
+      </c>
     </row>
     <row r="173">
       <c r="A173" t="inlineStr">
@@ -28095,6 +28651,7 @@
           <t>正常</t>
         </is>
       </c>
+      <c r="BD173" t="inlineStr"/>
     </row>
     <row r="174">
       <c r="A174" t="inlineStr">
@@ -28247,6 +28804,11 @@
       <c r="BC174" t="inlineStr">
         <is>
           <t>正常</t>
+        </is>
+      </c>
+      <c r="BD174" t="inlineStr">
+        <is>
+          <t>XSD20260127004I</t>
         </is>
       </c>
     </row>
@@ -28398,6 +28960,7 @@
           <t>关闭</t>
         </is>
       </c>
+      <c r="BD175" t="inlineStr"/>
     </row>
     <row r="176">
       <c r="A176" t="inlineStr">
@@ -28572,6 +29135,11 @@
           <t>正常</t>
         </is>
       </c>
+      <c r="BD176" t="inlineStr">
+        <is>
+          <t>XSD20260127005I</t>
+        </is>
+      </c>
     </row>
     <row r="177">
       <c r="A177" t="inlineStr">
@@ -28726,6 +29294,11 @@
           <t>正常</t>
         </is>
       </c>
+      <c r="BD177" t="inlineStr">
+        <is>
+          <t>XSD20260128005I</t>
+        </is>
+      </c>
     </row>
     <row r="178">
       <c r="A178" t="inlineStr">
@@ -28880,6 +29453,11 @@
           <t>正常</t>
         </is>
       </c>
+      <c r="BD178" t="inlineStr">
+        <is>
+          <t>XSD20260128006I</t>
+        </is>
+      </c>
     </row>
     <row r="179">
       <c r="A179" t="inlineStr">
@@ -29054,6 +29632,11 @@
           <t>正常</t>
         </is>
       </c>
+      <c r="BD179" t="inlineStr">
+        <is>
+          <t>XSD20260128007I</t>
+        </is>
+      </c>
     </row>
     <row r="180">
       <c r="A180" t="inlineStr">
@@ -29228,6 +29811,11 @@
           <t>正常</t>
         </is>
       </c>
+      <c r="BD180" t="inlineStr">
+        <is>
+          <t>XSD20260128008I</t>
+        </is>
+      </c>
     </row>
     <row r="181">
       <c r="A181" t="inlineStr">
@@ -29382,6 +29970,11 @@
           <t>正常</t>
         </is>
       </c>
+      <c r="BD181" t="inlineStr">
+        <is>
+          <t>XSD20260128009I</t>
+        </is>
+      </c>
     </row>
     <row r="182">
       <c r="A182" t="inlineStr">
@@ -29546,6 +30139,11 @@
           <t>正常</t>
         </is>
       </c>
+      <c r="BD182" t="inlineStr">
+        <is>
+          <t>XSD20260130005A</t>
+        </is>
+      </c>
     </row>
     <row r="183">
       <c r="A183" t="inlineStr">
@@ -29710,6 +30308,11 @@
           <t>正常</t>
         </is>
       </c>
+      <c r="BD183" t="inlineStr">
+        <is>
+          <t>XSD20260130000I</t>
+        </is>
+      </c>
     </row>
     <row r="184">
       <c r="A184" t="inlineStr">
@@ -29874,6 +30477,11 @@
           <t>正常</t>
         </is>
       </c>
+      <c r="BD184" t="inlineStr">
+        <is>
+          <t>XSD20260129003I</t>
+        </is>
+      </c>
     </row>
     <row r="185">
       <c r="A185" t="inlineStr">
@@ -30028,6 +30636,11 @@
           <t>正常</t>
         </is>
       </c>
+      <c r="BD185" t="inlineStr">
+        <is>
+          <t>XSD20260131000I</t>
+        </is>
+      </c>
     </row>
     <row r="186">
       <c r="A186" t="inlineStr">
@@ -30192,6 +30805,11 @@
           <t>正常</t>
         </is>
       </c>
+      <c r="BD186" t="inlineStr">
+        <is>
+          <t>XSD20260131009A</t>
+        </is>
+      </c>
     </row>
     <row r="187">
       <c r="A187" t="inlineStr">
@@ -30346,6 +30964,11 @@
           <t>正常</t>
         </is>
       </c>
+      <c r="BD187" t="inlineStr">
+        <is>
+          <t>XSD20260201003I</t>
+        </is>
+      </c>
     </row>
     <row r="188">
       <c r="A188" t="inlineStr">
@@ -30518,6 +31141,11 @@
       <c r="BC188" t="inlineStr">
         <is>
           <t>正常</t>
+        </is>
+      </c>
+      <c r="BD188" t="inlineStr">
+        <is>
+          <t>XSD20260202002A</t>
         </is>
       </c>
     </row>
@@ -30669,6 +31297,7 @@
           <t>关闭</t>
         </is>
       </c>
+      <c r="BD189" t="inlineStr"/>
     </row>
     <row r="190">
       <c r="A190" t="inlineStr">
@@ -30823,6 +31452,11 @@
           <t>正常</t>
         </is>
       </c>
+      <c r="BD190" t="inlineStr">
+        <is>
+          <t>XSD20260204007</t>
+        </is>
+      </c>
     </row>
     <row r="191">
       <c r="A191" t="inlineStr">
@@ -31028,6 +31662,11 @@
           <t>正常</t>
         </is>
       </c>
+      <c r="BD191" t="inlineStr">
+        <is>
+          <t>XSD20260204006</t>
+        </is>
+      </c>
     </row>
     <row r="192">
       <c r="A192" t="inlineStr">
@@ -31202,6 +31841,11 @@
           <t>正常</t>
         </is>
       </c>
+      <c r="BD192" t="inlineStr">
+        <is>
+          <t>XSD20260204004</t>
+        </is>
+      </c>
     </row>
     <row r="193">
       <c r="A193" t="inlineStr">
@@ -31356,6 +32000,11 @@
           <t>正常</t>
         </is>
       </c>
+      <c r="BD193" t="inlineStr">
+        <is>
+          <t>XSD20260205011I</t>
+        </is>
+      </c>
     </row>
     <row r="194">
       <c r="A194" t="inlineStr">
@@ -31520,6 +32169,11 @@
           <t>正常</t>
         </is>
       </c>
+      <c r="BD194" t="inlineStr">
+        <is>
+          <t>XSD20260205015I</t>
+        </is>
+      </c>
     </row>
     <row r="195">
       <c r="A195" t="inlineStr">
@@ -31679,6 +32333,11 @@
           <t>正常</t>
         </is>
       </c>
+      <c r="BD195" t="inlineStr">
+        <is>
+          <t>XSD20260205016I</t>
+        </is>
+      </c>
     </row>
     <row r="196">
       <c r="A196" t="inlineStr">
@@ -31853,6 +32512,11 @@
           <t>正常</t>
         </is>
       </c>
+      <c r="BD196" t="inlineStr">
+        <is>
+          <t>XSD20260205017A</t>
+        </is>
+      </c>
     </row>
     <row r="197">
       <c r="A197" t="inlineStr">
@@ -32007,6 +32671,11 @@
           <t>正常</t>
         </is>
       </c>
+      <c r="BD197" t="inlineStr">
+        <is>
+          <t>XSD20260207000I</t>
+        </is>
+      </c>
     </row>
     <row r="198">
       <c r="A198" t="inlineStr">
@@ -32181,6 +32850,11 @@
           <t>正常</t>
         </is>
       </c>
+      <c r="BD198" t="inlineStr">
+        <is>
+          <t>XSD20260207003A</t>
+        </is>
+      </c>
     </row>
     <row r="199">
       <c r="A199" t="inlineStr">
@@ -32381,6 +33055,11 @@
           <t>正常</t>
         </is>
       </c>
+      <c r="BD199" t="inlineStr">
+        <is>
+          <t>XSD20260207005A</t>
+        </is>
+      </c>
     </row>
     <row r="200">
       <c r="A200" t="inlineStr">
@@ -32555,6 +33234,11 @@
           <t>正常</t>
         </is>
       </c>
+      <c r="BD200" t="inlineStr">
+        <is>
+          <t>XSD20260207006A</t>
+        </is>
+      </c>
     </row>
     <row r="201">
       <c r="A201" t="inlineStr">
@@ -32729,6 +33413,11 @@
           <t>正常</t>
         </is>
       </c>
+      <c r="BD201" t="inlineStr">
+        <is>
+          <t>XSD20260207007I</t>
+        </is>
+      </c>
     </row>
     <row r="202">
       <c r="A202" t="inlineStr">
@@ -32883,6 +33572,11 @@
           <t>正常</t>
         </is>
       </c>
+      <c r="BD202" t="inlineStr">
+        <is>
+          <t>XSD20260208004I</t>
+        </is>
+      </c>
     </row>
     <row r="203">
       <c r="A203" t="inlineStr">
@@ -33057,6 +33751,7 @@
           <t>正常</t>
         </is>
       </c>
+      <c r="BD203" t="inlineStr"/>
     </row>
     <row r="204">
       <c r="A204" t="inlineStr">
@@ -33211,6 +33906,11 @@
           <t>正常</t>
         </is>
       </c>
+      <c r="BD204" t="inlineStr">
+        <is>
+          <t>XSD20260208012I</t>
+        </is>
+      </c>
     </row>
     <row r="205">
       <c r="A205" t="inlineStr">
@@ -33385,6 +34085,7 @@
           <t>正常</t>
         </is>
       </c>
+      <c r="BD205" t="inlineStr"/>
     </row>
     <row r="206">
       <c r="A206" t="inlineStr">
@@ -33549,6 +34250,7 @@
           <t>正常</t>
         </is>
       </c>
+      <c r="BD206" t="inlineStr"/>
     </row>
     <row r="207">
       <c r="A207" t="inlineStr">
@@ -33723,6 +34425,7 @@
           <t>正常</t>
         </is>
       </c>
+      <c r="BD207" t="inlineStr"/>
     </row>
     <row r="208">
       <c r="A208" t="inlineStr">
@@ -33872,6 +34575,11 @@
           <t>关闭</t>
         </is>
       </c>
+      <c r="BD208" t="inlineStr">
+        <is>
+          <t>XSD20260210003I</t>
+        </is>
+      </c>
     </row>
     <row r="209">
       <c r="A209" t="inlineStr">
@@ -34046,6 +34754,7 @@
           <t>正常</t>
         </is>
       </c>
+      <c r="BD209" t="inlineStr"/>
     </row>
     <row r="210">
       <c r="A210" t="inlineStr">
@@ -34220,6 +34929,11 @@
           <t>正常</t>
         </is>
       </c>
+      <c r="BD210" t="inlineStr">
+        <is>
+          <t>XSD20260211004A</t>
+        </is>
+      </c>
     </row>
     <row r="211">
       <c r="A211" t="inlineStr">
@@ -34394,6 +35108,11 @@
           <t>正常</t>
         </is>
       </c>
+      <c r="BD211" t="inlineStr">
+        <is>
+          <t>XSD20260212000I</t>
+        </is>
+      </c>
     </row>
     <row r="212">
       <c r="A212" t="inlineStr">
@@ -34548,6 +35267,11 @@
           <t>正常</t>
         </is>
       </c>
+      <c r="BD212" t="inlineStr">
+        <is>
+          <t>XSD20260212004I</t>
+        </is>
+      </c>
     </row>
     <row r="213">
       <c r="A213" t="inlineStr">
@@ -34722,6 +35446,11 @@
           <t>正常</t>
         </is>
       </c>
+      <c r="BD213" t="inlineStr">
+        <is>
+          <t>XSD20260212005I</t>
+        </is>
+      </c>
     </row>
     <row r="214">
       <c r="A214" t="inlineStr">
@@ -34886,6 +35615,11 @@
           <t>正常</t>
         </is>
       </c>
+      <c r="BD214" t="inlineStr">
+        <is>
+          <t>XSD20260212010I</t>
+        </is>
+      </c>
     </row>
     <row r="215">
       <c r="A215" t="inlineStr">
@@ -35060,6 +35794,11 @@
           <t>正常</t>
         </is>
       </c>
+      <c r="BD215" t="inlineStr">
+        <is>
+          <t>XSD20260213003A</t>
+        </is>
+      </c>
     </row>
     <row r="216">
       <c r="A216" t="inlineStr">
@@ -35222,6 +35961,11 @@
       <c r="BC216" t="inlineStr">
         <is>
           <t>正常</t>
+        </is>
+      </c>
+      <c r="BD216" t="inlineStr">
+        <is>
+          <t>XSD20260213004A</t>
         </is>
       </c>
     </row>
@@ -35373,6 +36117,11 @@
           <t>关闭</t>
         </is>
       </c>
+      <c r="BD217" t="inlineStr">
+        <is>
+          <t>XSD20260214001I</t>
+        </is>
+      </c>
     </row>
     <row r="218">
       <c r="A218" t="inlineStr">
@@ -35547,6 +36296,7 @@
           <t>正常</t>
         </is>
       </c>
+      <c r="BD218" t="inlineStr"/>
     </row>
     <row r="219">
       <c r="A219" t="inlineStr">
@@ -35721,6 +36471,11 @@
           <t>正常</t>
         </is>
       </c>
+      <c r="BD219" t="inlineStr">
+        <is>
+          <t>XSD20260215003I</t>
+        </is>
+      </c>
     </row>
     <row r="220">
       <c r="A220" t="inlineStr">
@@ -35895,6 +36650,11 @@
           <t>正常</t>
         </is>
       </c>
+      <c r="BD220" t="inlineStr">
+        <is>
+          <t>XSD20260215006A</t>
+        </is>
+      </c>
     </row>
     <row r="221">
       <c r="A221" t="inlineStr">
@@ -36059,6 +36819,11 @@
           <t>正常</t>
         </is>
       </c>
+      <c r="BD221" t="inlineStr">
+        <is>
+          <t>XSD20260216001I</t>
+        </is>
+      </c>
     </row>
     <row r="222">
       <c r="A222" t="inlineStr">
@@ -36233,6 +36998,11 @@
           <t>正常</t>
         </is>
       </c>
+      <c r="BD222" t="inlineStr">
+        <is>
+          <t>XSD20260217001I</t>
+        </is>
+      </c>
     </row>
     <row r="223">
       <c r="A223" t="inlineStr">
@@ -36387,6 +37157,11 @@
           <t>正常</t>
         </is>
       </c>
+      <c r="BD223" t="inlineStr">
+        <is>
+          <t>XSD20260217000I</t>
+        </is>
+      </c>
     </row>
     <row r="224">
       <c r="A224" t="inlineStr">
@@ -36561,6 +37336,11 @@
           <t>正常</t>
         </is>
       </c>
+      <c r="BD224" t="inlineStr">
+        <is>
+          <t>XSD20260217002I</t>
+        </is>
+      </c>
     </row>
     <row r="225">
       <c r="A225" t="inlineStr">
@@ -36715,6 +37495,11 @@
           <t>正常</t>
         </is>
       </c>
+      <c r="BD225" t="inlineStr">
+        <is>
+          <t>XSD20260217003I</t>
+        </is>
+      </c>
     </row>
     <row r="226">
       <c r="A226" t="inlineStr">
@@ -36889,6 +37674,11 @@
           <t>正常</t>
         </is>
       </c>
+      <c r="BD226" t="inlineStr">
+        <is>
+          <t>XSD20260219003I</t>
+        </is>
+      </c>
     </row>
     <row r="227">
       <c r="A227" t="inlineStr">
@@ -37063,6 +37853,11 @@
           <t>正常</t>
         </is>
       </c>
+      <c r="BD227" t="inlineStr">
+        <is>
+          <t>XSD20260219004I</t>
+        </is>
+      </c>
     </row>
     <row r="228">
       <c r="A228" t="inlineStr">
@@ -37237,6 +38032,11 @@
           <t>正常</t>
         </is>
       </c>
+      <c r="BD228" t="inlineStr">
+        <is>
+          <t>XSD20260219005I</t>
+        </is>
+      </c>
     </row>
     <row r="229">
       <c r="A229" t="inlineStr">
@@ -37401,6 +38201,11 @@
           <t>正常</t>
         </is>
       </c>
+      <c r="BD229" t="inlineStr">
+        <is>
+          <t>XSD20260219002I</t>
+        </is>
+      </c>
     </row>
     <row r="230">
       <c r="A230" t="inlineStr">
@@ -37575,6 +38380,11 @@
           <t>正常</t>
         </is>
       </c>
+      <c r="BD230" t="inlineStr">
+        <is>
+          <t>XSD20260219001I</t>
+        </is>
+      </c>
     </row>
     <row r="231">
       <c r="A231" t="inlineStr">
@@ -37744,6 +38554,11 @@
           <t>正常</t>
         </is>
       </c>
+      <c r="BD231" t="inlineStr">
+        <is>
+          <t>XSD20260221005I</t>
+        </is>
+      </c>
     </row>
     <row r="232">
       <c r="A232" t="inlineStr">
@@ -37906,6 +38721,11 @@
       <c r="BC232" t="inlineStr">
         <is>
           <t>正常</t>
+        </is>
+      </c>
+      <c r="BD232" t="inlineStr">
+        <is>
+          <t>XSD20260221004I</t>
         </is>
       </c>
     </row>
@@ -38057,6 +38877,7 @@
           <t>关闭</t>
         </is>
       </c>
+      <c r="BD233" t="inlineStr"/>
     </row>
     <row r="234">
       <c r="A234" t="inlineStr">
@@ -38211,6 +39032,11 @@
           <t>正常</t>
         </is>
       </c>
+      <c r="BD234" t="inlineStr">
+        <is>
+          <t>XSD20260221003I</t>
+        </is>
+      </c>
     </row>
     <row r="235">
       <c r="A235" t="inlineStr">
@@ -38375,6 +39201,7 @@
           <t>正常</t>
         </is>
       </c>
+      <c r="BD235" t="inlineStr"/>
     </row>
     <row r="236">
       <c r="A236" t="inlineStr">
@@ -38539,6 +39366,11 @@
           <t>正常</t>
         </is>
       </c>
+      <c r="BD236" t="inlineStr">
+        <is>
+          <t>XSD20260222000I</t>
+        </is>
+      </c>
     </row>
     <row r="237">
       <c r="A237" t="inlineStr">
@@ -38683,6 +39515,7 @@
           <t>正常</t>
         </is>
       </c>
+      <c r="BD237" t="inlineStr"/>
     </row>
     <row r="238">
       <c r="A238" t="inlineStr">
@@ -38857,6 +39690,11 @@
           <t>正常</t>
         </is>
       </c>
+      <c r="BD238" t="inlineStr">
+        <is>
+          <t>XSD20260224002I</t>
+        </is>
+      </c>
     </row>
     <row r="239">
       <c r="A239" t="inlineStr">
@@ -39021,6 +39859,11 @@
           <t>正常</t>
         </is>
       </c>
+      <c r="BD239" t="inlineStr">
+        <is>
+          <t>XSD20260302002I</t>
+        </is>
+      </c>
     </row>
     <row r="240">
       <c r="A240" t="inlineStr">
@@ -39195,6 +40038,11 @@
           <t>正常</t>
         </is>
       </c>
+      <c r="BD240" t="inlineStr">
+        <is>
+          <t>XSD20260302003I</t>
+        </is>
+      </c>
     </row>
     <row r="241">
       <c r="A241" t="inlineStr">
@@ -39367,6 +40215,11 @@
       <c r="BC241" t="inlineStr">
         <is>
           <t>正常</t>
+        </is>
+      </c>
+      <c r="BD241" t="inlineStr">
+        <is>
+          <t>XSD20260302005I</t>
         </is>
       </c>
     </row>
@@ -39518,6 +40371,7 @@
           <t>关闭</t>
         </is>
       </c>
+      <c r="BD242" t="inlineStr"/>
     </row>
     <row r="243">
       <c r="A243" t="inlineStr">
@@ -39692,6 +40546,11 @@
           <t>正常</t>
         </is>
       </c>
+      <c r="BD243" t="inlineStr">
+        <is>
+          <t>XSD20260302006I</t>
+        </is>
+      </c>
     </row>
     <row r="244">
       <c r="A244" t="inlineStr">
@@ -39866,6 +40725,11 @@
           <t>正常</t>
         </is>
       </c>
+      <c r="BD244" t="inlineStr">
+        <is>
+          <t>XSD20260302018I</t>
+        </is>
+      </c>
     </row>
     <row r="245">
       <c r="A245" t="inlineStr">
@@ -40040,6 +40904,11 @@
           <t>正常</t>
         </is>
       </c>
+      <c r="BD245" t="inlineStr">
+        <is>
+          <t>XSD20260304003A</t>
+        </is>
+      </c>
     </row>
     <row r="246">
       <c r="A246" t="inlineStr">
@@ -40214,6 +41083,11 @@
           <t>正常</t>
         </is>
       </c>
+      <c r="BD246" t="inlineStr">
+        <is>
+          <t>XSD20260304004A</t>
+        </is>
+      </c>
     </row>
     <row r="247">
       <c r="A247" t="inlineStr">
@@ -40388,6 +41262,11 @@
           <t>正常</t>
         </is>
       </c>
+      <c r="BD247" t="inlineStr">
+        <is>
+          <t>XSD20260305002I</t>
+        </is>
+      </c>
     </row>
     <row r="248">
       <c r="A248" t="inlineStr">
@@ -40562,6 +41441,11 @@
           <t>正常</t>
         </is>
       </c>
+      <c r="BD248" t="inlineStr">
+        <is>
+          <t>XSD20260306003I</t>
+        </is>
+      </c>
     </row>
     <row r="249">
       <c r="A249" t="inlineStr">
@@ -40726,6 +41610,11 @@
           <t>正常</t>
         </is>
       </c>
+      <c r="BD249" t="inlineStr">
+        <is>
+          <t>XSD20260306005I</t>
+        </is>
+      </c>
     </row>
     <row r="250">
       <c r="A250" t="inlineStr">
@@ -40900,6 +41789,11 @@
           <t>正常</t>
         </is>
       </c>
+      <c r="BD250" t="inlineStr">
+        <is>
+          <t>XSD20260307002I</t>
+        </is>
+      </c>
     </row>
     <row r="251">
       <c r="A251" t="inlineStr">
@@ -41064,6 +41958,11 @@
           <t>正常</t>
         </is>
       </c>
+      <c r="BD251" t="inlineStr">
+        <is>
+          <t>XSD20260309000I</t>
+        </is>
+      </c>
     </row>
     <row r="252">
       <c r="A252" t="inlineStr">
@@ -41238,6 +42137,11 @@
           <t>正常</t>
         </is>
       </c>
+      <c r="BD252" t="inlineStr">
+        <is>
+          <t>XSD20260310000A</t>
+        </is>
+      </c>
     </row>
     <row r="253">
       <c r="A253" t="inlineStr">
@@ -41412,6 +42316,11 @@
           <t>正常</t>
         </is>
       </c>
+      <c r="BD253" t="inlineStr">
+        <is>
+          <t>XSD20260310001A</t>
+        </is>
+      </c>
     </row>
     <row r="254">
       <c r="A254" t="inlineStr">
@@ -41586,6 +42495,11 @@
           <t>正常</t>
         </is>
       </c>
+      <c r="BD254" t="inlineStr">
+        <is>
+          <t>XSD20260310002A</t>
+        </is>
+      </c>
     </row>
     <row r="255">
       <c r="A255" t="inlineStr">
@@ -41760,6 +42674,11 @@
           <t>正常</t>
         </is>
       </c>
+      <c r="BD255" t="inlineStr">
+        <is>
+          <t>XSD20260312001I</t>
+        </is>
+      </c>
     </row>
     <row r="256">
       <c r="A256" t="inlineStr">
@@ -41934,6 +42853,11 @@
           <t>正常</t>
         </is>
       </c>
+      <c r="BD256" t="inlineStr">
+        <is>
+          <t>XSD20260312002I</t>
+        </is>
+      </c>
     </row>
     <row r="257">
       <c r="A257" t="inlineStr">
@@ -42088,6 +43012,11 @@
           <t>正常</t>
         </is>
       </c>
+      <c r="BD257" t="inlineStr">
+        <is>
+          <t>XSD20260315000I</t>
+        </is>
+      </c>
     </row>
     <row r="258">
       <c r="A258" t="inlineStr">
@@ -42262,6 +43191,7 @@
           <t>正常</t>
         </is>
       </c>
+      <c r="BD258" t="inlineStr"/>
     </row>
     <row r="259">
       <c r="A259" t="inlineStr">
@@ -42416,6 +43346,11 @@
           <t>正常</t>
         </is>
       </c>
+      <c r="BD259" t="inlineStr">
+        <is>
+          <t>XSD20260322000I</t>
+        </is>
+      </c>
     </row>
     <row r="260">
       <c r="A260" t="inlineStr">
@@ -42580,6 +43515,7 @@
           <t>正常</t>
         </is>
       </c>
+      <c r="BD260" t="inlineStr"/>
     </row>
     <row r="261">
       <c r="A261" t="inlineStr">
@@ -42729,6 +43665,7 @@
           <t>关闭</t>
         </is>
       </c>
+      <c r="BD261" t="inlineStr"/>
     </row>
     <row r="262">
       <c r="A262" t="inlineStr">
@@ -42881,6 +43818,11 @@
       <c r="BC262" t="inlineStr">
         <is>
           <t>正常</t>
+        </is>
+      </c>
+      <c r="BD262" t="inlineStr">
+        <is>
+          <t>XSD20260408000I</t>
         </is>
       </c>
     </row>
@@ -43000,8 +43942,6 @@
           <t>POS机刷卡</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr"/>
-      <c r="E2" t="inlineStr"/>
       <c r="F2" t="inlineStr">
         <is>
           <t>2025-10-10</t>
@@ -43036,8 +43976,6 @@
           <t>POS机刷卡</t>
         </is>
       </c>
-      <c r="D3" t="inlineStr"/>
-      <c r="E3" t="inlineStr"/>
       <c r="F3" t="inlineStr">
         <is>
           <t>2025-10-10</t>
@@ -43072,7 +44010,6 @@
           <t>支付宝</t>
         </is>
       </c>
-      <c r="D4" t="inlineStr"/>
       <c r="E4" t="inlineStr">
         <is>
           <t>2088002319285895</t>
@@ -43112,7 +44049,6 @@
           <t>支付宝</t>
         </is>
       </c>
-      <c r="D5" t="inlineStr"/>
       <c r="E5" t="inlineStr">
         <is>
           <t>2088002319285895</t>
@@ -43196,7 +44132,6 @@
           <t>支付宝</t>
         </is>
       </c>
-      <c r="D7" t="inlineStr"/>
       <c r="E7" t="inlineStr">
         <is>
           <t>2088002319285895</t>
@@ -43236,7 +44171,6 @@
           <t>支付宝</t>
         </is>
       </c>
-      <c r="D8" t="inlineStr"/>
       <c r="E8" t="inlineStr">
         <is>
           <t>2088002319285895</t>
@@ -43276,8 +44210,6 @@
           <t>现金</t>
         </is>
       </c>
-      <c r="D9" t="inlineStr"/>
-      <c r="E9" t="inlineStr"/>
       <c r="F9" t="inlineStr">
         <is>
           <t>2025-10-11</t>
@@ -43312,8 +44244,6 @@
           <t>京东收银</t>
         </is>
       </c>
-      <c r="D10" t="inlineStr"/>
-      <c r="E10" t="inlineStr"/>
       <c r="F10" t="inlineStr">
         <is>
           <t>2025-10-11</t>
@@ -43348,8 +44278,6 @@
           <t>京东收银</t>
         </is>
       </c>
-      <c r="D11" t="inlineStr"/>
-      <c r="E11" t="inlineStr"/>
       <c r="F11" t="inlineStr">
         <is>
           <t>2025-10-11</t>
@@ -43384,8 +44312,6 @@
           <t>京东收银</t>
         </is>
       </c>
-      <c r="D12" t="inlineStr"/>
-      <c r="E12" t="inlineStr"/>
       <c r="F12" t="inlineStr">
         <is>
           <t>2025-10-11</t>
@@ -43420,8 +44346,6 @@
           <t>京东收银</t>
         </is>
       </c>
-      <c r="D13" t="inlineStr"/>
-      <c r="E13" t="inlineStr"/>
       <c r="F13" t="inlineStr">
         <is>
           <t>2025-10-11</t>
@@ -43456,8 +44380,6 @@
           <t>京东收银</t>
         </is>
       </c>
-      <c r="D14" t="inlineStr"/>
-      <c r="E14" t="inlineStr"/>
       <c r="F14" t="inlineStr">
         <is>
           <t>2025-10-11</t>
@@ -43536,8 +44458,6 @@
           <t>微信支付</t>
         </is>
       </c>
-      <c r="D16" t="inlineStr"/>
-      <c r="E16" t="inlineStr"/>
       <c r="F16" t="inlineStr">
         <is>
           <t>2025-10-12</t>
@@ -43572,8 +44492,6 @@
           <t>微信支付</t>
         </is>
       </c>
-      <c r="D17" t="inlineStr"/>
-      <c r="E17" t="inlineStr"/>
       <c r="F17" t="inlineStr">
         <is>
           <t>2025-10-12</t>
@@ -43696,7 +44614,6 @@
           <t>支付宝</t>
         </is>
       </c>
-      <c r="D20" t="inlineStr"/>
       <c r="E20" t="inlineStr">
         <is>
           <t>2088002319285895</t>
@@ -44088,8 +45005,6 @@
           <t>微信转账</t>
         </is>
       </c>
-      <c r="D29" t="inlineStr"/>
-      <c r="E29" t="inlineStr"/>
       <c r="F29" t="inlineStr">
         <is>
           <t>2025-10-29</t>
@@ -44124,8 +45039,6 @@
           <t>微信转账</t>
         </is>
       </c>
-      <c r="D30" t="inlineStr"/>
-      <c r="E30" t="inlineStr"/>
       <c r="F30" t="inlineStr">
         <is>
           <t>2025-10-29</t>
@@ -44160,8 +45073,6 @@
           <t>微信转账</t>
         </is>
       </c>
-      <c r="D31" t="inlineStr"/>
-      <c r="E31" t="inlineStr"/>
       <c r="F31" t="inlineStr">
         <is>
           <t>2025-10-31</t>
@@ -44284,8 +45195,6 @@
           <t>微信转账</t>
         </is>
       </c>
-      <c r="D34" t="inlineStr"/>
-      <c r="E34" t="inlineStr"/>
       <c r="F34" t="inlineStr">
         <is>
           <t>2025-11-09</t>
@@ -44408,8 +45317,6 @@
           <t>微信转账</t>
         </is>
       </c>
-      <c r="D37" t="inlineStr"/>
-      <c r="E37" t="inlineStr"/>
       <c r="F37" t="inlineStr">
         <is>
           <t>2025-11-17</t>
@@ -44444,8 +45351,6 @@
           <t>微信转账</t>
         </is>
       </c>
-      <c r="D38" t="inlineStr"/>
-      <c r="E38" t="inlineStr"/>
       <c r="F38" t="inlineStr">
         <is>
           <t>2025-11-17</t>
@@ -44480,8 +45385,6 @@
           <t>微信转账</t>
         </is>
       </c>
-      <c r="D39" t="inlineStr"/>
-      <c r="E39" t="inlineStr"/>
       <c r="F39" t="inlineStr">
         <is>
           <t>2025-11-23</t>
@@ -44648,7 +45551,6 @@
           <t>支付宝</t>
         </is>
       </c>
-      <c r="D43" t="inlineStr"/>
       <c r="E43" t="inlineStr">
         <is>
           <t>2088002225541092</t>
@@ -44732,7 +45634,6 @@
           <t>支付宝</t>
         </is>
       </c>
-      <c r="D45" t="inlineStr"/>
       <c r="E45" t="inlineStr">
         <is>
           <t>2088002994467188</t>
@@ -44860,7 +45761,6 @@
           <t>支付宝</t>
         </is>
       </c>
-      <c r="D48" t="inlineStr"/>
       <c r="E48" t="inlineStr">
         <is>
           <t>2088902961157316</t>
@@ -44988,8 +45888,6 @@
           <t>微信转账</t>
         </is>
       </c>
-      <c r="D51" t="inlineStr"/>
-      <c r="E51" t="inlineStr"/>
       <c r="F51" t="inlineStr">
         <is>
           <t>2025-12-02</t>
@@ -45024,8 +45922,6 @@
           <t>微信转账</t>
         </is>
       </c>
-      <c r="D52" t="inlineStr"/>
-      <c r="E52" t="inlineStr"/>
       <c r="F52" t="inlineStr">
         <is>
           <t>2025-12-02</t>
@@ -45060,8 +45956,6 @@
           <t>微信转账</t>
         </is>
       </c>
-      <c r="D53" t="inlineStr"/>
-      <c r="E53" t="inlineStr"/>
       <c r="F53" t="inlineStr">
         <is>
           <t>2025-12-02</t>
@@ -45096,7 +45990,6 @@
           <t>支付宝</t>
         </is>
       </c>
-      <c r="D54" t="inlineStr"/>
       <c r="E54" t="inlineStr">
         <is>
           <t>2088002994467188</t>
@@ -45268,8 +46161,6 @@
           <t>微信转账</t>
         </is>
       </c>
-      <c r="D58" t="inlineStr"/>
-      <c r="E58" t="inlineStr"/>
       <c r="F58" t="inlineStr">
         <is>
           <t>2025-12-08</t>
@@ -45304,8 +46195,6 @@
           <t>京东收银</t>
         </is>
       </c>
-      <c r="D59" t="inlineStr"/>
-      <c r="E59" t="inlineStr"/>
       <c r="F59" t="inlineStr">
         <is>
           <t>2025-12-10</t>
@@ -45428,8 +46317,6 @@
           <t>京东收银</t>
         </is>
       </c>
-      <c r="D62" t="inlineStr"/>
-      <c r="E62" t="inlineStr"/>
       <c r="F62" t="inlineStr">
         <is>
           <t>2025-12-13</t>
@@ -45464,8 +46351,6 @@
           <t>京东收银</t>
         </is>
       </c>
-      <c r="D63" t="inlineStr"/>
-      <c r="E63" t="inlineStr"/>
       <c r="F63" t="inlineStr">
         <is>
           <t>2025-12-13</t>
@@ -45588,8 +46473,6 @@
           <t>微信转账</t>
         </is>
       </c>
-      <c r="D66" t="inlineStr"/>
-      <c r="E66" t="inlineStr"/>
       <c r="F66" t="inlineStr">
         <is>
           <t>2025-12-14</t>
@@ -45624,8 +46507,6 @@
           <t>微信转账</t>
         </is>
       </c>
-      <c r="D67" t="inlineStr"/>
-      <c r="E67" t="inlineStr"/>
       <c r="F67" t="inlineStr">
         <is>
           <t>2025-12-16</t>
@@ -45660,8 +46541,6 @@
           <t>微信转账</t>
         </is>
       </c>
-      <c r="D68" t="inlineStr"/>
-      <c r="E68" t="inlineStr"/>
       <c r="F68" t="inlineStr">
         <is>
           <t>2025-12-16</t>
@@ -45696,8 +46575,6 @@
           <t>京东收银</t>
         </is>
       </c>
-      <c r="D69" t="inlineStr"/>
-      <c r="E69" t="inlineStr"/>
       <c r="F69" t="inlineStr">
         <is>
           <t>2025-12-17</t>
@@ -45732,8 +46609,6 @@
           <t>银行转账</t>
         </is>
       </c>
-      <c r="D70" t="inlineStr"/>
-      <c r="E70" t="inlineStr"/>
       <c r="F70" t="inlineStr">
         <is>
           <t>2025-12-18</t>
@@ -46032,8 +46907,6 @@
           <t>微信转账</t>
         </is>
       </c>
-      <c r="D77" t="inlineStr"/>
-      <c r="E77" t="inlineStr"/>
       <c r="F77" t="inlineStr">
         <is>
           <t>2025-12-21</t>
@@ -46068,7 +46941,6 @@
           <t>支付宝</t>
         </is>
       </c>
-      <c r="D78" t="inlineStr"/>
       <c r="E78" t="inlineStr">
         <is>
           <t>2088832401405643</t>
@@ -46152,8 +47024,6 @@
           <t>微信转账</t>
         </is>
       </c>
-      <c r="D80" t="inlineStr"/>
-      <c r="E80" t="inlineStr"/>
       <c r="F80" t="inlineStr">
         <is>
           <t>2025-12-23</t>
@@ -46188,8 +47058,6 @@
           <t>微信转账</t>
         </is>
       </c>
-      <c r="D81" t="inlineStr"/>
-      <c r="E81" t="inlineStr"/>
       <c r="F81" t="inlineStr">
         <is>
           <t>2025-12-23</t>
@@ -46224,8 +47092,6 @@
           <t>微信转账</t>
         </is>
       </c>
-      <c r="D82" t="inlineStr"/>
-      <c r="E82" t="inlineStr"/>
       <c r="F82" t="inlineStr">
         <is>
           <t>2025-12-23</t>
@@ -46568,8 +47434,6 @@
           <t>微信转账</t>
         </is>
       </c>
-      <c r="D90" t="inlineStr"/>
-      <c r="E90" t="inlineStr"/>
       <c r="F90" t="inlineStr">
         <is>
           <t>2025-12-28</t>
@@ -46604,8 +47468,6 @@
           <t>微信转账</t>
         </is>
       </c>
-      <c r="D91" t="inlineStr"/>
-      <c r="E91" t="inlineStr"/>
       <c r="F91" t="inlineStr">
         <is>
           <t>2025-12-28</t>
@@ -46640,8 +47502,6 @@
           <t>微信转账</t>
         </is>
       </c>
-      <c r="D92" t="inlineStr"/>
-      <c r="E92" t="inlineStr"/>
       <c r="F92" t="inlineStr">
         <is>
           <t>2025-12-29</t>
@@ -46720,7 +47580,6 @@
           <t>支付宝</t>
         </is>
       </c>
-      <c r="D94" t="inlineStr"/>
       <c r="E94" t="inlineStr">
         <is>
           <t>2088002319285895</t>
@@ -47156,8 +48015,6 @@
           <t>微信转账</t>
         </is>
       </c>
-      <c r="D104" t="inlineStr"/>
-      <c r="E104" t="inlineStr"/>
       <c r="F104" t="inlineStr">
         <is>
           <t>2026-01-08</t>
@@ -47192,8 +48049,6 @@
           <t>现金</t>
         </is>
       </c>
-      <c r="D105" t="inlineStr"/>
-      <c r="E105" t="inlineStr"/>
       <c r="F105" t="inlineStr">
         <is>
           <t>2026-01-08</t>
@@ -47448,8 +48303,6 @@
           <t>支付宝布乖</t>
         </is>
       </c>
-      <c r="D111" t="inlineStr"/>
-      <c r="E111" t="inlineStr"/>
       <c r="F111" t="inlineStr">
         <is>
           <t>2026-01-14</t>
@@ -47484,7 +48337,6 @@
           <t>支付宝</t>
         </is>
       </c>
-      <c r="D112" t="inlineStr"/>
       <c r="E112" t="inlineStr">
         <is>
           <t>2088222192105510</t>
@@ -47700,8 +48552,6 @@
           <t>现金</t>
         </is>
       </c>
-      <c r="D117" t="inlineStr"/>
-      <c r="E117" t="inlineStr"/>
       <c r="F117" t="inlineStr">
         <is>
           <t>2026-01-24</t>
@@ -47956,8 +48806,6 @@
           <t>微信转账</t>
         </is>
       </c>
-      <c r="D123" t="inlineStr"/>
-      <c r="E123" t="inlineStr"/>
       <c r="F123" t="inlineStr">
         <is>
           <t>2026-01-27</t>
@@ -48036,8 +48884,6 @@
           <t>现金</t>
         </is>
       </c>
-      <c r="D125" t="inlineStr"/>
-      <c r="E125" t="inlineStr"/>
       <c r="F125" t="inlineStr">
         <is>
           <t>2026-01-28</t>
@@ -48072,8 +48918,6 @@
           <t>现金</t>
         </is>
       </c>
-      <c r="D126" t="inlineStr"/>
-      <c r="E126" t="inlineStr"/>
       <c r="F126" t="inlineStr">
         <is>
           <t>2026-01-28</t>
@@ -48196,8 +49040,6 @@
           <t>现金</t>
         </is>
       </c>
-      <c r="D129" t="inlineStr"/>
-      <c r="E129" t="inlineStr"/>
       <c r="F129" t="inlineStr">
         <is>
           <t>2026-01-28</t>
@@ -48232,7 +49074,6 @@
           <t>支付宝</t>
         </is>
       </c>
-      <c r="D130" t="inlineStr"/>
       <c r="E130" t="inlineStr">
         <is>
           <t>2088032410269735</t>
@@ -48272,8 +49113,6 @@
           <t>微信转账</t>
         </is>
       </c>
-      <c r="D131" t="inlineStr"/>
-      <c r="E131" t="inlineStr"/>
       <c r="F131" t="inlineStr">
         <is>
           <t>2026-01-30</t>
@@ -48308,8 +49147,6 @@
           <t>微信转账</t>
         </is>
       </c>
-      <c r="D132" t="inlineStr"/>
-      <c r="E132" t="inlineStr"/>
       <c r="F132" t="inlineStr">
         <is>
           <t>2026-01-30</t>
@@ -48388,8 +49225,6 @@
           <t>现金</t>
         </is>
       </c>
-      <c r="D134" t="inlineStr"/>
-      <c r="E134" t="inlineStr"/>
       <c r="F134" t="inlineStr">
         <is>
           <t>2026-01-31</t>
@@ -48424,8 +49259,6 @@
           <t>微信转账</t>
         </is>
       </c>
-      <c r="D135" t="inlineStr"/>
-      <c r="E135" t="inlineStr"/>
       <c r="F135" t="inlineStr">
         <is>
           <t>2026-02-01</t>
@@ -48504,8 +49337,6 @@
           <t>微信转账</t>
         </is>
       </c>
-      <c r="D137" t="inlineStr"/>
-      <c r="E137" t="inlineStr"/>
       <c r="F137" t="inlineStr">
         <is>
           <t>2026-02-03</t>
@@ -48646,8 +49477,6 @@
           <t>微信转账</t>
         </is>
       </c>
-      <c r="D140" t="inlineStr"/>
-      <c r="E140" t="inlineStr"/>
       <c r="F140" t="inlineStr">
         <is>
           <t>2026-02-05</t>
@@ -48726,8 +49555,6 @@
           <t>微信转账</t>
         </is>
       </c>
-      <c r="D142" t="inlineStr"/>
-      <c r="E142" t="inlineStr"/>
       <c r="F142" t="inlineStr">
         <is>
           <t>2026-02-05</t>
@@ -48806,8 +49633,6 @@
           <t>微信转账</t>
         </is>
       </c>
-      <c r="D144" t="inlineStr"/>
-      <c r="E144" t="inlineStr"/>
       <c r="F144" t="inlineStr">
         <is>
           <t>2026-02-07</t>
@@ -49036,8 +49861,6 @@
           <t>微信转账</t>
         </is>
       </c>
-      <c r="D149" t="inlineStr"/>
-      <c r="E149" t="inlineStr"/>
       <c r="F149" t="inlineStr">
         <is>
           <t>2026-02-08</t>
@@ -49116,8 +49939,6 @@
           <t>微信转账</t>
         </is>
       </c>
-      <c r="D151" t="inlineStr"/>
-      <c r="E151" t="inlineStr"/>
       <c r="F151" t="inlineStr">
         <is>
           <t>2026-02-08</t>
@@ -49196,7 +50017,6 @@
           <t>支付宝</t>
         </is>
       </c>
-      <c r="D153" t="inlineStr"/>
       <c r="E153" t="inlineStr">
         <is>
           <t>2088512265361247</t>
@@ -49412,8 +50232,6 @@
           <t>微信转账</t>
         </is>
       </c>
-      <c r="D158" t="inlineStr"/>
-      <c r="E158" t="inlineStr"/>
       <c r="F158" t="inlineStr">
         <is>
           <t>2026-02-12</t>
@@ -49492,7 +50310,6 @@
           <t>支付宝</t>
         </is>
       </c>
-      <c r="D160" t="inlineStr"/>
       <c r="E160" t="inlineStr">
         <is>
           <t>2088302372758544</t>
@@ -49576,7 +50393,6 @@
           <t>支付宝</t>
         </is>
       </c>
-      <c r="D162" t="inlineStr"/>
       <c r="E162" t="inlineStr">
         <is>
           <t>2088702206388077</t>
@@ -49748,8 +50564,6 @@
           <t>微信转账</t>
         </is>
       </c>
-      <c r="D166" t="inlineStr"/>
-      <c r="E166" t="inlineStr"/>
       <c r="F166" t="inlineStr">
         <is>
           <t>2026-02-16</t>
@@ -49828,8 +50642,6 @@
           <t>微信转账</t>
         </is>
       </c>
-      <c r="D168" t="inlineStr"/>
-      <c r="E168" t="inlineStr"/>
       <c r="F168" t="inlineStr">
         <is>
           <t>2026-02-17</t>
@@ -50172,7 +50984,6 @@
           <t>支付宝</t>
         </is>
       </c>
-      <c r="D176" t="inlineStr"/>
       <c r="E176" t="inlineStr">
         <is>
           <t>2088902389212451</t>
@@ -50212,7 +51023,6 @@
           <t>支付宝</t>
         </is>
       </c>
-      <c r="D177" t="inlineStr"/>
       <c r="E177" t="inlineStr">
         <is>
           <t>2088902389212451</t>
@@ -50340,7 +51150,6 @@
           <t>支付宝</t>
         </is>
       </c>
-      <c r="D180" t="inlineStr"/>
       <c r="E180" t="inlineStr">
         <is>
           <t>2088632081302755</t>
@@ -50380,7 +51189,6 @@
           <t>支付宝</t>
         </is>
       </c>
-      <c r="D181" t="inlineStr"/>
       <c r="E181" t="inlineStr">
         <is>
           <t>2088642749888550</t>
@@ -50464,7 +51272,6 @@
           <t>支付宝</t>
         </is>
       </c>
-      <c r="D183" t="inlineStr"/>
       <c r="E183" t="inlineStr">
         <is>
           <t>2088702933886053</t>
@@ -50856,8 +51663,6 @@
           <t>微信转账</t>
         </is>
       </c>
-      <c r="D192" t="inlineStr"/>
-      <c r="E192" t="inlineStr"/>
       <c r="F192" t="inlineStr">
         <is>
           <t>2026-03-06</t>
@@ -50936,8 +51741,6 @@
           <t>微信转账</t>
         </is>
       </c>
-      <c r="D194" t="inlineStr"/>
-      <c r="E194" t="inlineStr"/>
       <c r="F194" t="inlineStr">
         <is>
           <t>2026-03-09</t>
@@ -51280,8 +52083,6 @@
           <t>支付宝布乖</t>
         </is>
       </c>
-      <c r="D202" t="inlineStr"/>
-      <c r="E202" t="inlineStr"/>
       <c r="F202" t="inlineStr">
         <is>
           <t>2026-03-22</t>
@@ -51316,8 +52117,6 @@
           <t>京东收银</t>
         </is>
       </c>
-      <c r="D203" t="inlineStr"/>
-      <c r="E203" t="inlineStr"/>
       <c r="F203" t="inlineStr">
         <is>
           <t>2026-03-23</t>
@@ -51352,8 +52151,6 @@
           <t>微信转账</t>
         </is>
       </c>
-      <c r="D204" t="inlineStr"/>
-      <c r="E204" t="inlineStr"/>
       <c r="F204" t="inlineStr">
         <is>
           <t>2026-04-08</t>
@@ -51495,8 +52292,6 @@
           <t>POS机刷卡</t>
         </is>
       </c>
-      <c r="C2" t="inlineStr"/>
-      <c r="D2" t="inlineStr"/>
       <c r="E2" t="inlineStr">
         <is>
           <t>支付</t>
@@ -51527,8 +52322,6 @@
           <t>POS机刷卡</t>
         </is>
       </c>
-      <c r="C3" t="inlineStr"/>
-      <c r="D3" t="inlineStr"/>
       <c r="E3" t="inlineStr">
         <is>
           <t>支付</t>
@@ -51559,7 +52352,6 @@
           <t>支付宝</t>
         </is>
       </c>
-      <c r="C4" t="inlineStr"/>
       <c r="D4" t="inlineStr">
         <is>
           <t>QJ_LS_251010_00007_ZF_05</t>
@@ -51595,7 +52387,6 @@
           <t>支付宝</t>
         </is>
       </c>
-      <c r="C5" t="inlineStr"/>
       <c r="D5" t="inlineStr">
         <is>
           <t>QJ_LS_251010_00005_ZF_01</t>
@@ -51631,7 +52422,6 @@
           <t>支付宝</t>
         </is>
       </c>
-      <c r="C6" t="inlineStr"/>
       <c r="D6" t="inlineStr">
         <is>
           <t>QJ_LS_251011_00004_ZF_02</t>
@@ -51667,7 +52457,6 @@
           <t>支付宝</t>
         </is>
       </c>
-      <c r="C7" t="inlineStr"/>
       <c r="D7" t="inlineStr">
         <is>
           <t>QJ_LS_251011_00005_ZF_01</t>
@@ -51703,8 +52492,6 @@
           <t>现金</t>
         </is>
       </c>
-      <c r="C8" t="inlineStr"/>
-      <c r="D8" t="inlineStr"/>
       <c r="E8" t="inlineStr">
         <is>
           <t>支付</t>
@@ -51735,8 +52522,6 @@
           <t>京东收银</t>
         </is>
       </c>
-      <c r="C9" t="inlineStr"/>
-      <c r="D9" t="inlineStr"/>
       <c r="E9" t="inlineStr">
         <is>
           <t>支付</t>
@@ -51767,8 +52552,6 @@
           <t>京东收银</t>
         </is>
       </c>
-      <c r="C10" t="inlineStr"/>
-      <c r="D10" t="inlineStr"/>
       <c r="E10" t="inlineStr">
         <is>
           <t>支付</t>
@@ -51799,8 +52582,6 @@
           <t>京东收银</t>
         </is>
       </c>
-      <c r="C11" t="inlineStr"/>
-      <c r="D11" t="inlineStr"/>
       <c r="E11" t="inlineStr">
         <is>
           <t>支付</t>
@@ -51831,8 +52612,6 @@
           <t>京东收银</t>
         </is>
       </c>
-      <c r="C12" t="inlineStr"/>
-      <c r="D12" t="inlineStr"/>
       <c r="E12" t="inlineStr">
         <is>
           <t>支付</t>
@@ -51863,8 +52642,6 @@
           <t>京东收银</t>
         </is>
       </c>
-      <c r="C13" t="inlineStr"/>
-      <c r="D13" t="inlineStr"/>
       <c r="E13" t="inlineStr">
         <is>
           <t>支付</t>
@@ -51975,7 +52752,6 @@
           <t>微信支付</t>
         </is>
       </c>
-      <c r="C16" t="inlineStr"/>
       <c r="D16" t="inlineStr">
         <is>
           <t>QJ_LS_251012_00011_ZF_02</t>
@@ -52011,7 +52787,6 @@
           <t>微信支付</t>
         </is>
       </c>
-      <c r="C17" t="inlineStr"/>
       <c r="D17" t="inlineStr">
         <is>
           <t>QJ_LS_251012_00014_ZF_02</t>
@@ -52127,7 +52902,6 @@
           <t>支付宝</t>
         </is>
       </c>
-      <c r="C20" t="inlineStr"/>
       <c r="D20" t="inlineStr">
         <is>
           <t>QJ_LS_251012_00020_ZF_01</t>
@@ -52483,8 +53257,6 @@
           <t>微信转账</t>
         </is>
       </c>
-      <c r="C29" t="inlineStr"/>
-      <c r="D29" t="inlineStr"/>
       <c r="E29" t="inlineStr">
         <is>
           <t>支付</t>
@@ -52515,8 +53287,6 @@
           <t>微信转账</t>
         </is>
       </c>
-      <c r="C30" t="inlineStr"/>
-      <c r="D30" t="inlineStr"/>
       <c r="E30" t="inlineStr">
         <is>
           <t>支付</t>
@@ -52547,8 +53317,6 @@
           <t>微信转账</t>
         </is>
       </c>
-      <c r="C31" t="inlineStr"/>
-      <c r="D31" t="inlineStr"/>
       <c r="E31" t="inlineStr">
         <is>
           <t>支付</t>
@@ -52659,8 +53427,6 @@
           <t>微信转账</t>
         </is>
       </c>
-      <c r="C34" t="inlineStr"/>
-      <c r="D34" t="inlineStr"/>
       <c r="E34" t="inlineStr">
         <is>
           <t>支付</t>
@@ -52771,8 +53537,6 @@
           <t>微信转账</t>
         </is>
       </c>
-      <c r="C37" t="inlineStr"/>
-      <c r="D37" t="inlineStr"/>
       <c r="E37" t="inlineStr">
         <is>
           <t>支付</t>
@@ -52803,8 +53567,6 @@
           <t>微信转账</t>
         </is>
       </c>
-      <c r="C38" t="inlineStr"/>
-      <c r="D38" t="inlineStr"/>
       <c r="E38" t="inlineStr">
         <is>
           <t>支付</t>
@@ -52835,8 +53597,6 @@
           <t>微信转账</t>
         </is>
       </c>
-      <c r="C39" t="inlineStr"/>
-      <c r="D39" t="inlineStr"/>
       <c r="E39" t="inlineStr">
         <is>
           <t>支付</t>
@@ -52987,7 +53747,6 @@
           <t>支付宝</t>
         </is>
       </c>
-      <c r="C43" t="inlineStr"/>
       <c r="D43" t="inlineStr">
         <is>
           <t>QJ_LS_251126_00002_ZF_02</t>
@@ -53063,7 +53822,6 @@
           <t>支付宝</t>
         </is>
       </c>
-      <c r="C45" t="inlineStr"/>
       <c r="D45" t="inlineStr">
         <is>
           <t>QJ_LS_251127_00001_ZF_01</t>
@@ -53219,7 +53977,6 @@
           <t>支付宝</t>
         </is>
       </c>
-      <c r="C49" t="inlineStr"/>
       <c r="D49" t="inlineStr">
         <is>
           <t>QJ_LS_251128_00003_ZF_01</t>
@@ -53335,8 +54092,6 @@
           <t>微信转账</t>
         </is>
       </c>
-      <c r="C52" t="inlineStr"/>
-      <c r="D52" t="inlineStr"/>
       <c r="E52" t="inlineStr">
         <is>
           <t>支付</t>
@@ -53367,8 +54122,6 @@
           <t>微信转账</t>
         </is>
       </c>
-      <c r="C53" t="inlineStr"/>
-      <c r="D53" t="inlineStr"/>
       <c r="E53" t="inlineStr">
         <is>
           <t>支付</t>
@@ -53399,8 +54152,6 @@
           <t>微信转账</t>
         </is>
       </c>
-      <c r="C54" t="inlineStr"/>
-      <c r="D54" t="inlineStr"/>
       <c r="E54" t="inlineStr">
         <is>
           <t>支付</t>
@@ -53431,7 +54182,6 @@
           <t>支付宝</t>
         </is>
       </c>
-      <c r="C55" t="inlineStr"/>
       <c r="D55" t="inlineStr">
         <is>
           <t>QJ_LS_251203_00001_ZF_01</t>
@@ -53587,8 +54337,6 @@
           <t>微信转账</t>
         </is>
       </c>
-      <c r="C59" t="inlineStr"/>
-      <c r="D59" t="inlineStr"/>
       <c r="E59" t="inlineStr">
         <is>
           <t>支付</t>
@@ -53619,8 +54367,6 @@
           <t>京东收银</t>
         </is>
       </c>
-      <c r="C60" t="inlineStr"/>
-      <c r="D60" t="inlineStr"/>
       <c r="E60" t="inlineStr">
         <is>
           <t>支付</t>
@@ -53731,8 +54477,6 @@
           <t>京东收银</t>
         </is>
       </c>
-      <c r="C63" t="inlineStr"/>
-      <c r="D63" t="inlineStr"/>
       <c r="E63" t="inlineStr">
         <is>
           <t>支付</t>
@@ -53763,8 +54507,6 @@
           <t>京东收银</t>
         </is>
       </c>
-      <c r="C64" t="inlineStr"/>
-      <c r="D64" t="inlineStr"/>
       <c r="E64" t="inlineStr">
         <is>
           <t>支付</t>
@@ -53875,8 +54617,6 @@
           <t>微信转账</t>
         </is>
       </c>
-      <c r="C67" t="inlineStr"/>
-      <c r="D67" t="inlineStr"/>
       <c r="E67" t="inlineStr">
         <is>
           <t>支付</t>
@@ -53907,8 +54647,6 @@
           <t>微信转账</t>
         </is>
       </c>
-      <c r="C68" t="inlineStr"/>
-      <c r="D68" t="inlineStr"/>
       <c r="E68" t="inlineStr">
         <is>
           <t>支付</t>
@@ -53939,8 +54677,6 @@
           <t>微信转账</t>
         </is>
       </c>
-      <c r="C69" t="inlineStr"/>
-      <c r="D69" t="inlineStr"/>
       <c r="E69" t="inlineStr">
         <is>
           <t>支付</t>
@@ -53971,8 +54707,6 @@
           <t>京东收银</t>
         </is>
       </c>
-      <c r="C70" t="inlineStr"/>
-      <c r="D70" t="inlineStr"/>
       <c r="E70" t="inlineStr">
         <is>
           <t>支付</t>
@@ -54003,8 +54737,6 @@
           <t>银行转账</t>
         </is>
       </c>
-      <c r="C71" t="inlineStr"/>
-      <c r="D71" t="inlineStr"/>
       <c r="E71" t="inlineStr">
         <is>
           <t>支付</t>
@@ -54275,8 +55007,6 @@
           <t>微信转账</t>
         </is>
       </c>
-      <c r="C78" t="inlineStr"/>
-      <c r="D78" t="inlineStr"/>
       <c r="E78" t="inlineStr">
         <is>
           <t>支付</t>
@@ -54307,7 +55037,6 @@
           <t>支付宝</t>
         </is>
       </c>
-      <c r="C79" t="inlineStr"/>
       <c r="D79" t="inlineStr">
         <is>
           <t>QJ_LS_251222_00002_ZF_01</t>
@@ -54383,8 +55112,6 @@
           <t>微信转账</t>
         </is>
       </c>
-      <c r="C81" t="inlineStr"/>
-      <c r="D81" t="inlineStr"/>
       <c r="E81" t="inlineStr">
         <is>
           <t>支付</t>
@@ -54415,8 +55142,6 @@
           <t>微信转账</t>
         </is>
       </c>
-      <c r="C82" t="inlineStr"/>
-      <c r="D82" t="inlineStr"/>
       <c r="E82" t="inlineStr">
         <is>
           <t>支付</t>
@@ -54447,8 +55172,6 @@
           <t>微信转账</t>
         </is>
       </c>
-      <c r="C83" t="inlineStr"/>
-      <c r="D83" t="inlineStr"/>
       <c r="E83" t="inlineStr">
         <is>
           <t>支付</t>
@@ -54759,8 +55482,6 @@
           <t>微信转账</t>
         </is>
       </c>
-      <c r="C91" t="inlineStr"/>
-      <c r="D91" t="inlineStr"/>
       <c r="E91" t="inlineStr">
         <is>
           <t>支付</t>
@@ -54791,8 +55512,6 @@
           <t>微信转账</t>
         </is>
       </c>
-      <c r="C92" t="inlineStr"/>
-      <c r="D92" t="inlineStr"/>
       <c r="E92" t="inlineStr">
         <is>
           <t>支付</t>
@@ -54823,8 +55542,6 @@
           <t>微信转账</t>
         </is>
       </c>
-      <c r="C93" t="inlineStr"/>
-      <c r="D93" t="inlineStr"/>
       <c r="E93" t="inlineStr">
         <is>
           <t>支付</t>
@@ -54895,7 +55612,6 @@
           <t>支付宝</t>
         </is>
       </c>
-      <c r="C95" t="inlineStr"/>
       <c r="D95" t="inlineStr">
         <is>
           <t>QJ_LS_251231_00002_ZF_01</t>
@@ -55291,8 +56007,6 @@
           <t>微信转账</t>
         </is>
       </c>
-      <c r="C105" t="inlineStr"/>
-      <c r="D105" t="inlineStr"/>
       <c r="E105" t="inlineStr">
         <is>
           <t>支付</t>
@@ -55323,8 +56037,6 @@
           <t>现金</t>
         </is>
       </c>
-      <c r="C106" t="inlineStr"/>
-      <c r="D106" t="inlineStr"/>
       <c r="E106" t="inlineStr">
         <is>
           <t>支付</t>
@@ -55555,8 +56267,6 @@
           <t>支付宝布乖</t>
         </is>
       </c>
-      <c r="C112" t="inlineStr"/>
-      <c r="D112" t="inlineStr"/>
       <c r="E112" t="inlineStr">
         <is>
           <t>支付</t>
@@ -55587,7 +56297,6 @@
           <t>支付宝</t>
         </is>
       </c>
-      <c r="C113" t="inlineStr"/>
       <c r="D113" t="inlineStr">
         <is>
           <t>QJ_LS_260116_00001_ZF_01</t>
@@ -55783,8 +56492,6 @@
           <t>现金</t>
         </is>
       </c>
-      <c r="C118" t="inlineStr"/>
-      <c r="D118" t="inlineStr"/>
       <c r="E118" t="inlineStr">
         <is>
           <t>支付</t>
@@ -56015,8 +56722,6 @@
           <t>微信转账</t>
         </is>
       </c>
-      <c r="C124" t="inlineStr"/>
-      <c r="D124" t="inlineStr"/>
       <c r="E124" t="inlineStr">
         <is>
           <t>支付</t>
@@ -56087,8 +56792,6 @@
           <t>现金</t>
         </is>
       </c>
-      <c r="C126" t="inlineStr"/>
-      <c r="D126" t="inlineStr"/>
       <c r="E126" t="inlineStr">
         <is>
           <t>支付</t>
@@ -56119,8 +56822,6 @@
           <t>现金</t>
         </is>
       </c>
-      <c r="C127" t="inlineStr"/>
-      <c r="D127" t="inlineStr"/>
       <c r="E127" t="inlineStr">
         <is>
           <t>支付</t>
@@ -56231,8 +56932,6 @@
           <t>现金</t>
         </is>
       </c>
-      <c r="C130" t="inlineStr"/>
-      <c r="D130" t="inlineStr"/>
       <c r="E130" t="inlineStr">
         <is>
           <t>支付</t>
@@ -56263,7 +56962,6 @@
           <t>支付宝</t>
         </is>
       </c>
-      <c r="C131" t="inlineStr"/>
       <c r="D131" t="inlineStr">
         <is>
           <t>QJ_LS_260130_00001_ZF_01</t>
@@ -56299,8 +56997,6 @@
           <t>微信转账</t>
         </is>
       </c>
-      <c r="C132" t="inlineStr"/>
-      <c r="D132" t="inlineStr"/>
       <c r="E132" t="inlineStr">
         <is>
           <t>支付</t>
@@ -56331,8 +57027,6 @@
           <t>微信转账</t>
         </is>
       </c>
-      <c r="C133" t="inlineStr"/>
-      <c r="D133" t="inlineStr"/>
       <c r="E133" t="inlineStr">
         <is>
           <t>支付</t>
@@ -56403,8 +57097,6 @@
           <t>现金</t>
         </is>
       </c>
-      <c r="C135" t="inlineStr"/>
-      <c r="D135" t="inlineStr"/>
       <c r="E135" t="inlineStr">
         <is>
           <t>支付</t>
@@ -56435,8 +57127,6 @@
           <t>微信转账</t>
         </is>
       </c>
-      <c r="C136" t="inlineStr"/>
-      <c r="D136" t="inlineStr"/>
       <c r="E136" t="inlineStr">
         <is>
           <t>支付</t>
@@ -56507,8 +57197,6 @@
           <t>微信转账</t>
         </is>
       </c>
-      <c r="C138" t="inlineStr"/>
-      <c r="D138" t="inlineStr"/>
       <c r="E138" t="inlineStr">
         <is>
           <t>支付</t>
@@ -56659,8 +57347,6 @@
           <t>微信转账</t>
         </is>
       </c>
-      <c r="C142" t="inlineStr"/>
-      <c r="D142" t="inlineStr"/>
       <c r="E142" t="inlineStr">
         <is>
           <t>支付</t>
@@ -56731,8 +57417,6 @@
           <t>微信转账</t>
         </is>
       </c>
-      <c r="C144" t="inlineStr"/>
-      <c r="D144" t="inlineStr"/>
       <c r="E144" t="inlineStr">
         <is>
           <t>支付</t>
@@ -56803,8 +57487,6 @@
           <t>微信转账</t>
         </is>
       </c>
-      <c r="C146" t="inlineStr"/>
-      <c r="D146" t="inlineStr"/>
       <c r="E146" t="inlineStr">
         <is>
           <t>支付</t>
@@ -57035,8 +57717,6 @@
           <t>微信转账</t>
         </is>
       </c>
-      <c r="C152" t="inlineStr"/>
-      <c r="D152" t="inlineStr"/>
       <c r="E152" t="inlineStr">
         <is>
           <t>支付</t>
@@ -57107,8 +57787,6 @@
           <t>微信转账</t>
         </is>
       </c>
-      <c r="C154" t="inlineStr"/>
-      <c r="D154" t="inlineStr"/>
       <c r="E154" t="inlineStr">
         <is>
           <t>支付</t>
@@ -57179,7 +57857,6 @@
           <t>支付宝</t>
         </is>
       </c>
-      <c r="C156" t="inlineStr"/>
       <c r="D156" t="inlineStr">
         <is>
           <t>QJ_LS_260209_00002_ZF_01</t>
@@ -57375,8 +58052,6 @@
           <t>微信转账</t>
         </is>
       </c>
-      <c r="C161" t="inlineStr"/>
-      <c r="D161" t="inlineStr"/>
       <c r="E161" t="inlineStr">
         <is>
           <t>支付</t>
@@ -57447,7 +58122,6 @@
           <t>支付宝</t>
         </is>
       </c>
-      <c r="C163" t="inlineStr"/>
       <c r="D163" t="inlineStr">
         <is>
           <t>QJ_LS_260212_00004_ZF_02</t>
@@ -57523,7 +58197,6 @@
           <t>支付宝</t>
         </is>
       </c>
-      <c r="C165" t="inlineStr"/>
       <c r="D165" t="inlineStr">
         <is>
           <t>QJ_LS_260213_00002_ZF_01</t>
@@ -57679,8 +58352,6 @@
           <t>微信转账</t>
         </is>
       </c>
-      <c r="C169" t="inlineStr"/>
-      <c r="D169" t="inlineStr"/>
       <c r="E169" t="inlineStr">
         <is>
           <t>支付</t>
@@ -57751,8 +58422,6 @@
           <t>微信转账</t>
         </is>
       </c>
-      <c r="C171" t="inlineStr"/>
-      <c r="D171" t="inlineStr"/>
       <c r="E171" t="inlineStr">
         <is>
           <t>支付</t>
@@ -58063,7 +58732,6 @@
           <t>支付宝</t>
         </is>
       </c>
-      <c r="C179" t="inlineStr"/>
       <c r="D179" t="inlineStr">
         <is>
           <t>QJ_LS_260219_00003_ZF_01</t>
@@ -58099,7 +58767,6 @@
           <t>支付宝</t>
         </is>
       </c>
-      <c r="C180" t="inlineStr"/>
       <c r="D180" t="inlineStr">
         <is>
           <t>QJ_LS_260220_00001_ZF_01</t>
@@ -58215,7 +58882,6 @@
           <t>支付宝</t>
         </is>
       </c>
-      <c r="C183" t="inlineStr"/>
       <c r="D183" t="inlineStr">
         <is>
           <t>QJ_LS_260221_00003_ZF_01</t>
@@ -58251,7 +58917,6 @@
           <t>支付宝</t>
         </is>
       </c>
-      <c r="C184" t="inlineStr"/>
       <c r="D184" t="inlineStr">
         <is>
           <t>QJ_LS_260222_00001_ZF_02</t>
@@ -58327,7 +58992,6 @@
           <t>支付宝</t>
         </is>
       </c>
-      <c r="C186" t="inlineStr"/>
       <c r="D186" t="inlineStr">
         <is>
           <t>QJ_LS_260224_00002_ZF_01</t>
@@ -58683,8 +59347,6 @@
           <t>微信转账</t>
         </is>
       </c>
-      <c r="C195" t="inlineStr"/>
-      <c r="D195" t="inlineStr"/>
       <c r="E195" t="inlineStr">
         <is>
           <t>支付</t>
@@ -58755,8 +59417,6 @@
           <t>微信转账</t>
         </is>
       </c>
-      <c r="C197" t="inlineStr"/>
-      <c r="D197" t="inlineStr"/>
       <c r="E197" t="inlineStr">
         <is>
           <t>支付</t>
@@ -59067,8 +59727,6 @@
           <t>支付宝布乖</t>
         </is>
       </c>
-      <c r="C205" t="inlineStr"/>
-      <c r="D205" t="inlineStr"/>
       <c r="E205" t="inlineStr">
         <is>
           <t>支付</t>
@@ -59099,8 +59757,6 @@
           <t>京东收银</t>
         </is>
       </c>
-      <c r="C206" t="inlineStr"/>
-      <c r="D206" t="inlineStr"/>
       <c r="E206" t="inlineStr">
         <is>
           <t>支付</t>
@@ -59131,8 +59787,6 @@
           <t>微信转账</t>
         </is>
       </c>
-      <c r="C207" t="inlineStr"/>
-      <c r="D207" t="inlineStr"/>
       <c r="E207" t="inlineStr">
         <is>
           <t>支付</t>
